--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.83174599729196</v>
+        <v>5.010158724559944</v>
       </c>
       <c r="D2" t="n">
-        <v>34.13481749068838</v>
+        <v>5.546907842236863</v>
       </c>
       <c r="E2" t="n">
-        <v>1.250844571689857</v>
+        <v>0.2032622428996018</v>
       </c>
       <c r="F2" t="n">
-        <v>4.665627190559961</v>
+        <v>0.7581644184659937</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.04034242443023</v>
+        <v>5.044055643969912</v>
       </c>
       <c r="D3" t="n">
-        <v>23.42866164561386</v>
+        <v>3.807157517412252</v>
       </c>
       <c r="E3" t="n">
-        <v>1.250844571689857</v>
+        <v>0.2032622428996018</v>
       </c>
       <c r="F3" t="n">
-        <v>4.665627190559961</v>
+        <v>0.7581644184659937</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>33.58332966757062</v>
+        <v>5.457291070980227</v>
       </c>
       <c r="D4" t="n">
-        <v>32.24439998054336</v>
+        <v>5.239714996838296</v>
       </c>
       <c r="E4" t="n">
-        <v>1.250844571689857</v>
+        <v>0.2032622428996018</v>
       </c>
       <c r="F4" t="n">
-        <v>4.665627190559961</v>
+        <v>0.7581644184659937</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
